--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123623986</v>
+        <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
+        <v>89376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>822</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Slemringad vaxskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hygrophorus gliocyclus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattsarve, Gtl</t>
+          <t>Hardoj, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727202</v>
+        <v>727031</v>
       </c>
       <c r="R2" t="n">
-        <v>6370550</v>
+        <v>6370429</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,58 +784,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123623986</t>
+          <t>https://artportalen.se/Sighting/137333442</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623979</v>
+        <v>123623986</v>
       </c>
       <c r="B3" t="n">
-        <v>75428</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -895,7 +906,3591 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/123623986</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137333409</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96617</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>727103</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6370625</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333409</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137333411</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91935</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>727169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6370603</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333411</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137333426</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91592</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>727089</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6370403</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333426</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137333425</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87533</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>727082</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6370414</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333425</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137333439</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87533</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>727140</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6370282</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333439</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137333396</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87394</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>727073</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6371058</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333396</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137333429</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87370</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>727160</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6370416</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333429</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137333431</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87370</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>727178</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6370430</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333431</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137333419</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87615</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>727051</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6370425</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333419</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137333424</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87615</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>727071</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6370435</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333424</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137333399</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>727063</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6371061</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333399</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137333427</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>727124</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6370421</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333427</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137333422</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>727066</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6370456</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333422</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123623979</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mattsarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>727202</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6370550</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/123623979</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137333412</v>
+      </c>
+      <c r="B18" t="n">
+        <v>111718</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>727170</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6370607</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333412</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137333440</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111718</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>727137</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6370263</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333440</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137333443</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104949</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>727042</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6370557</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333443</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137333444</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104949</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>727015</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6370578</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333444</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137333414</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106557</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>727104</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6370552</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333414</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137333398</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92948</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>727091</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6371064</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333398</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137333410</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90101</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>727090</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6370618</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333410</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137333433</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87486</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>727127</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6370353</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Svavelgul mycelsträng.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333433</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137333434</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87486</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>727087</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6370283</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333434</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137333416</v>
+      </c>
+      <c r="B27" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>727073</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6370380</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333416</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137333423</v>
+      </c>
+      <c r="B28" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>727067</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6370440</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333423</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137333432</v>
+      </c>
+      <c r="B29" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>727139</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6370400</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333432</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137333436</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87570</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>727082</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6370278</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333436</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137333421</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87536</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>727047</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6370449</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333421</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137333435</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87536</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>727081</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6370280</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333435</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137333417</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90840</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6049769</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Clitopaxillus alexandri</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Gillet) G.Moreno &amp; al.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>727051</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6370387</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333417</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137333418</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90840</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6049769</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Clitopaxillus alexandri</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Gillet) G.Moreno &amp; al.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>727040</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6370391</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333418</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137333430</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93483</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Silkestaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hardoj, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>727158</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6370422</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137333430</t>
         </is>
       </c>
     </row>
@@ -903,6 +4498,38 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>89376</v>
+        <v>89379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137333425</v>
       </c>
       <c r="B7" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137333439</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137333396</v>
       </c>
       <c r="B9" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137333429</v>
       </c>
       <c r="B10" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>137333431</v>
       </c>
       <c r="B11" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137333419</v>
       </c>
       <c r="B12" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137333424</v>
       </c>
       <c r="B13" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104949</v>
+        <v>104954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104949</v>
+        <v>104954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92948</v>
+        <v>92951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>137333410</v>
       </c>
       <c r="B24" t="n">
-        <v>90101</v>
+        <v>90104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137333433</v>
       </c>
       <c r="B25" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137333434</v>
       </c>
       <c r="B26" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137333416</v>
       </c>
       <c r="B27" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>137333423</v>
       </c>
       <c r="B28" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137333432</v>
       </c>
       <c r="B29" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137333436</v>
       </c>
       <c r="B30" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137333421</v>
       </c>
       <c r="B31" t="n">
-        <v>87536</v>
+        <v>87539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137333435</v>
       </c>
       <c r="B32" t="n">
-        <v>87536</v>
+        <v>87539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137333417</v>
       </c>
       <c r="B33" t="n">
-        <v>90840</v>
+        <v>90843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137333418</v>
       </c>
       <c r="B34" t="n">
-        <v>90840</v>
+        <v>90843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93483</v>
+        <v>93488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104954</v>
+        <v>104957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104954</v>
+        <v>104957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92951</v>
+        <v>92953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93488</v>
+        <v>93490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>89379</v>
+        <v>89384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137333425</v>
       </c>
       <c r="B7" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137333439</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137333396</v>
       </c>
       <c r="B9" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137333429</v>
       </c>
       <c r="B10" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>137333431</v>
       </c>
       <c r="B11" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137333419</v>
       </c>
       <c r="B12" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137333424</v>
       </c>
       <c r="B13" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91565</v>
+        <v>91570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104957</v>
+        <v>104963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104957</v>
+        <v>104963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92953</v>
+        <v>92958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>137333410</v>
       </c>
       <c r="B24" t="n">
-        <v>90104</v>
+        <v>90109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137333433</v>
       </c>
       <c r="B25" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137333434</v>
       </c>
       <c r="B26" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137333416</v>
       </c>
       <c r="B27" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>137333423</v>
       </c>
       <c r="B28" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137333432</v>
       </c>
       <c r="B29" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137333436</v>
       </c>
       <c r="B30" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137333421</v>
       </c>
       <c r="B31" t="n">
-        <v>87539</v>
+        <v>87544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137333435</v>
       </c>
       <c r="B32" t="n">
-        <v>87539</v>
+        <v>87544</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137333417</v>
       </c>
       <c r="B33" t="n">
-        <v>90843</v>
+        <v>90848</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137333418</v>
       </c>
       <c r="B34" t="n">
-        <v>90843</v>
+        <v>90848</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93490</v>
+        <v>93496</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104963</v>
+        <v>104964</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104963</v>
+        <v>104964</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>89384</v>
+        <v>89395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137333425</v>
       </c>
       <c r="B7" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137333439</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137333396</v>
       </c>
       <c r="B9" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137333429</v>
       </c>
       <c r="B10" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>137333431</v>
       </c>
       <c r="B11" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137333419</v>
       </c>
       <c r="B12" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137333424</v>
       </c>
       <c r="B13" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91570</v>
+        <v>91582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104964</v>
+        <v>104976</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104964</v>
+        <v>104976</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92958</v>
+        <v>92970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>137333410</v>
       </c>
       <c r="B24" t="n">
-        <v>90109</v>
+        <v>90120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137333433</v>
       </c>
       <c r="B25" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137333434</v>
       </c>
       <c r="B26" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137333416</v>
       </c>
       <c r="B27" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>137333423</v>
       </c>
       <c r="B28" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137333432</v>
       </c>
       <c r="B29" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137333436</v>
       </c>
       <c r="B30" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137333421</v>
       </c>
       <c r="B31" t="n">
-        <v>87544</v>
+        <v>87555</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137333435</v>
       </c>
       <c r="B32" t="n">
-        <v>87544</v>
+        <v>87555</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137333417</v>
       </c>
       <c r="B33" t="n">
-        <v>90848</v>
+        <v>90859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137333418</v>
       </c>
       <c r="B34" t="n">
-        <v>90848</v>
+        <v>90859</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93496</v>
+        <v>93508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>89395</v>
+        <v>89396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137333425</v>
       </c>
       <c r="B7" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137333439</v>
       </c>
       <c r="B8" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137333396</v>
       </c>
       <c r="B9" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137333429</v>
       </c>
       <c r="B10" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>137333431</v>
       </c>
       <c r="B11" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137333419</v>
       </c>
       <c r="B12" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137333424</v>
       </c>
       <c r="B13" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91582</v>
+        <v>91583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104976</v>
+        <v>104977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104976</v>
+        <v>104977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>137333410</v>
       </c>
       <c r="B24" t="n">
-        <v>90120</v>
+        <v>90121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137333433</v>
       </c>
       <c r="B25" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137333434</v>
       </c>
       <c r="B26" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137333416</v>
       </c>
       <c r="B27" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>137333423</v>
       </c>
       <c r="B28" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137333432</v>
       </c>
       <c r="B29" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137333436</v>
       </c>
       <c r="B30" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137333421</v>
       </c>
       <c r="B31" t="n">
-        <v>87555</v>
+        <v>87556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137333435</v>
       </c>
       <c r="B32" t="n">
-        <v>87555</v>
+        <v>87556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137333417</v>
       </c>
       <c r="B33" t="n">
-        <v>90859</v>
+        <v>90860</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137333418</v>
       </c>
       <c r="B34" t="n">
-        <v>90859</v>
+        <v>90860</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93508</v>
+        <v>93509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>89396</v>
+        <v>89399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137333425</v>
       </c>
       <c r="B7" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137333439</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137333396</v>
       </c>
       <c r="B9" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137333429</v>
       </c>
       <c r="B10" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>137333431</v>
       </c>
       <c r="B11" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137333419</v>
       </c>
       <c r="B12" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137333424</v>
       </c>
       <c r="B13" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104977</v>
+        <v>104980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104977</v>
+        <v>104980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>137333410</v>
       </c>
       <c r="B24" t="n">
-        <v>90121</v>
+        <v>90124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137333433</v>
       </c>
       <c r="B25" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137333434</v>
       </c>
       <c r="B26" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137333416</v>
       </c>
       <c r="B27" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>137333423</v>
       </c>
       <c r="B28" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137333432</v>
       </c>
       <c r="B29" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137333436</v>
       </c>
       <c r="B30" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137333421</v>
       </c>
       <c r="B31" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137333435</v>
       </c>
       <c r="B32" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137333417</v>
       </c>
       <c r="B33" t="n">
-        <v>90860</v>
+        <v>90863</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137333418</v>
       </c>
       <c r="B34" t="n">
-        <v>90860</v>
+        <v>90863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93509</v>
+        <v>93512</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42798-2026 artfynd.xlsx
+++ b/artfynd/A 42798-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137333442</v>
       </c>
       <c r="B2" t="n">
-        <v>89399</v>
+        <v>89403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137333409</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137333411</v>
       </c>
       <c r="B5" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137333426</v>
       </c>
       <c r="B6" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>137333425</v>
       </c>
       <c r="B7" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137333439</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>137333396</v>
       </c>
       <c r="B9" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137333429</v>
       </c>
       <c r="B10" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>137333431</v>
       </c>
       <c r="B11" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137333419</v>
       </c>
       <c r="B12" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137333424</v>
       </c>
       <c r="B13" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>137333399</v>
       </c>
       <c r="B14" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137333427</v>
       </c>
       <c r="B15" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>137333422</v>
       </c>
       <c r="B16" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137333412</v>
       </c>
       <c r="B18" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137333440</v>
       </c>
       <c r="B19" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137333443</v>
       </c>
       <c r="B20" t="n">
-        <v>104980</v>
+        <v>104986</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>137333444</v>
       </c>
       <c r="B21" t="n">
-        <v>104980</v>
+        <v>104986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137333414</v>
       </c>
       <c r="B22" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>137333398</v>
       </c>
       <c r="B23" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>137333410</v>
       </c>
       <c r="B24" t="n">
-        <v>90124</v>
+        <v>90128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137333433</v>
       </c>
       <c r="B25" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137333434</v>
       </c>
       <c r="B26" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>137333416</v>
       </c>
       <c r="B27" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>137333423</v>
       </c>
       <c r="B28" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137333432</v>
       </c>
       <c r="B29" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137333436</v>
       </c>
       <c r="B30" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137333421</v>
       </c>
       <c r="B31" t="n">
-        <v>87559</v>
+        <v>87563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>137333435</v>
       </c>
       <c r="B32" t="n">
-        <v>87559</v>
+        <v>87563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>137333417</v>
       </c>
       <c r="B33" t="n">
-        <v>90863</v>
+        <v>90867</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>137333418</v>
       </c>
       <c r="B34" t="n">
-        <v>90863</v>
+        <v>90867</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>137333430</v>
       </c>
       <c r="B35" t="n">
-        <v>93512</v>
+        <v>93516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
